--- a/cet4/result/45_艺术女神_创业女王的传奇/45_艺术女神_创业女王的传奇_学习版.xlsx
+++ b/cet4/result/45_艺术女神_创业女王的传奇/45_艺术女神_创业女王的传奇_学习版.xlsx
@@ -399,724 +399,724 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>artist</v>
       </c>
       <c r="B2" t="str">
-        <v>artist</v>
+        <v>/ˈɑːrtɪst/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>艺术家</v>
       </c>
-      <c r="D2" t="str">
-        <v>artist(艺术家)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>zeal</v>
       </c>
       <c r="B3" t="str">
-        <v>zeal</v>
+        <v>/ziːl/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>热情</v>
       </c>
-      <c r="D3" t="str">
-        <v>zeal(热情)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>hatch</v>
       </c>
       <c r="B4" t="str">
-        <v>hatch</v>
+        <v>/hætʃ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D4" t="str">
         <v>孵化</v>
       </c>
-      <c r="D4" t="str">
-        <v>hatch(孵化)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>fresh</v>
       </c>
       <c r="B5" t="str">
-        <v>fresh</v>
+        <v>/freʃ/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>新鲜的</v>
       </c>
-      <c r="D5" t="str">
-        <v>fresh(新鲜的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>northwest</v>
       </c>
       <c r="B6" t="str">
-        <v>northwest</v>
+        <v>/ˌnɔːrθˈwest/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D6" t="str">
         <v>西北</v>
       </c>
-      <c r="D6" t="str">
-        <v>northwest(西北)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>platform</v>
       </c>
       <c r="B7" t="str">
-        <v>platform</v>
+        <v>/ˈplætfɔːrm/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>平台</v>
       </c>
-      <c r="D7" t="str">
-        <v>platform(平台)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>finance</v>
       </c>
       <c r="B8" t="str">
-        <v>finance</v>
+        <v>/ˈfaɪnæns/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>资金</v>
       </c>
-      <c r="D8" t="str">
-        <v>finance(资金)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>slum</v>
       </c>
       <c r="B9" t="str">
-        <v>slum</v>
+        <v>/slʌm/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D9" t="str">
         <v>贫民窟</v>
       </c>
-      <c r="D9" t="str">
-        <v>slum(贫民窟)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>necessarily</v>
       </c>
       <c r="B10" t="str">
-        <v>necessarily</v>
+        <v>/ˌnesəˈserəli/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D10" t="str">
         <v>必然地</v>
       </c>
-      <c r="D10" t="str">
-        <v>necessarily(必然地)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>measurable</v>
       </c>
       <c r="B11" t="str">
-        <v>measurable</v>
+        <v>/ˈmeʒərəbl/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>可测量的</v>
       </c>
-      <c r="D11" t="str">
-        <v>measurable(可测量的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>less</v>
       </c>
       <c r="B12" t="str">
-        <v>less</v>
+        <v>/les/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./v./adj./adv./prep.</v>
+      </c>
+      <c r="D12" t="str">
         <v>较少地</v>
       </c>
-      <c r="D12" t="str">
-        <v>less(较少地)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>oven</v>
       </c>
       <c r="B13" t="str">
-        <v>oven</v>
+        <v>/ˈʌvn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>烤箱</v>
       </c>
-      <c r="D13" t="str">
-        <v>oven(烤箱)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>mutton</v>
       </c>
       <c r="B14" t="str">
-        <v>mutton</v>
+        <v>/ˈmʌtn/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>羊肉</v>
       </c>
-      <c r="D14" t="str">
-        <v>mutton(羊肉)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>grant</v>
       </c>
       <c r="B15" t="str">
-        <v>grant</v>
+        <v>/ɡrænt/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D15" t="str">
         <v>拨款</v>
       </c>
-      <c r="D15" t="str">
-        <v>grant(拨款)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>explanation</v>
       </c>
       <c r="B16" t="str">
-        <v>explanation</v>
+        <v>/ˌekspləˈneɪʃn/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>解释</v>
       </c>
-      <c r="D16" t="str">
-        <v>explanation(解释)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>golden</v>
       </c>
       <c r="B17" t="str">
-        <v>golden</v>
+        <v>/ˈɡoʊldən/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>金色的</v>
       </c>
-      <c r="D17" t="str">
-        <v>golden(金色的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>tablet</v>
       </c>
       <c r="B18" t="str">
-        <v>tablet</v>
+        <v>/ˈtæblət/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>平板电脑</v>
       </c>
-      <c r="D18" t="str">
-        <v>tablet(平板电脑)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>individual</v>
       </c>
       <c r="B19" t="str">
-        <v>individual</v>
+        <v>/ˌɪndɪˈvɪdʒuəl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>个人</v>
       </c>
-      <c r="D19" t="str">
-        <v>individual(个人)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>procession</v>
       </c>
       <c r="B20" t="str">
-        <v>procession</v>
+        <v>/prəˈseʃn/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>队伍</v>
       </c>
-      <c r="D20" t="str">
-        <v>procession(队伍)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>likewise</v>
       </c>
       <c r="B21" t="str">
-        <v>likewise</v>
+        <v>/ˈlaɪkwaɪz/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D21" t="str">
         <v>同样地</v>
       </c>
-      <c r="D21" t="str">
-        <v>likewise(同样地)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>beautiful</v>
       </c>
       <c r="B22" t="str">
-        <v>beautiful</v>
+        <v>/ˈbjuːtɪfl/</v>
       </c>
       <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>美丽的</v>
       </c>
-      <c r="D22" t="str">
-        <v>beautiful(美丽的)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>mutual</v>
       </c>
       <c r="B23" t="str">
-        <v>mutual</v>
+        <v>/ˈmjuːtʃuəl/</v>
       </c>
       <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>相互的</v>
       </c>
-      <c r="D23" t="str">
-        <v>mutual(相互的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>instruct</v>
       </c>
       <c r="B24" t="str">
-        <v>instruct</v>
+        <v>/ɪnˈstrʌkt/</v>
       </c>
       <c r="C24" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D24" t="str">
         <v>指导</v>
       </c>
-      <c r="D24" t="str">
-        <v>instruct(指导)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>correction</v>
       </c>
       <c r="B25" t="str">
-        <v>correction</v>
+        <v>/kəˈrekʃn/</v>
       </c>
       <c r="C25" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>纠正</v>
       </c>
-      <c r="D25" t="str">
-        <v>correction(纠正)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>cream</v>
       </c>
       <c r="B26" t="str">
-        <v>cream</v>
+        <v>/kriːm/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>奶油</v>
       </c>
-      <c r="D26" t="str">
-        <v>cream(奶油)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>loudly</v>
       </c>
       <c r="B27" t="str">
-        <v>loudly</v>
+        <v>/ˈlaʊdli/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D27" t="str">
         <v>大声地</v>
       </c>
-      <c r="D27" t="str">
-        <v>loudly(大声地)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>gay</v>
       </c>
       <c r="B28" t="str">
-        <v>gay</v>
+        <v>/ɡeɪ/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>快乐的</v>
       </c>
-      <c r="D28" t="str">
-        <v>gay(快乐的)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>site</v>
       </c>
       <c r="B29" t="str">
-        <v>site</v>
+        <v>/saɪt/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D29" t="str">
         <v>地点</v>
       </c>
-      <c r="D29" t="str">
-        <v>site(地点)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>everybody</v>
       </c>
       <c r="B30" t="str">
-        <v>everybody</v>
+        <v>/ˈevribɑːdi,ˈevribʌdi/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D30" t="str">
         <v>每个人</v>
       </c>
-      <c r="D30" t="str">
-        <v>everybody(每个人)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>convey</v>
       </c>
       <c r="B31" t="str">
-        <v>convey</v>
+        <v>/kənˈveɪ/</v>
       </c>
       <c r="C31" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D31" t="str">
         <v>传达</v>
       </c>
-      <c r="D31" t="str">
-        <v>convey(传达)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>aviation</v>
       </c>
       <c r="B32" t="str">
-        <v>aviation</v>
+        <v>/ˌeɪviˈeɪʃn/</v>
       </c>
       <c r="C32" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>航空</v>
       </c>
-      <c r="D32" t="str">
-        <v>aviation(航空)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>presence</v>
       </c>
       <c r="B33" t="str">
-        <v>presence</v>
+        <v>/ˈprezns/</v>
       </c>
       <c r="C33" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>存在</v>
       </c>
-      <c r="D33" t="str">
-        <v>presence(存在)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>successfully</v>
       </c>
       <c r="B34" t="str">
-        <v>successfully</v>
+        <v>/səkˈsesfəli/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D34" t="str">
         <v>成功地</v>
       </c>
-      <c r="D34" t="str">
-        <v>successfully(成功地)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>undergo</v>
       </c>
       <c r="B35" t="str">
-        <v>undergo</v>
+        <v>/ˌʌndərˈɡoʊ/</v>
       </c>
       <c r="C35" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D35" t="str">
         <v>经历</v>
       </c>
-      <c r="D35" t="str">
-        <v>undergo(经历)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>deny</v>
       </c>
       <c r="B36" t="str">
-        <v>deny</v>
+        <v>/dɪˈnaɪ/</v>
       </c>
       <c r="C36" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D36" t="str">
         <v>否认</v>
       </c>
-      <c r="D36" t="str">
-        <v>deny(否认)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>prize</v>
       </c>
       <c r="B37" t="str">
-        <v>prize</v>
+        <v>/praɪz/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D37" t="str">
         <v>奖项</v>
       </c>
-      <c r="D37" t="str">
-        <v>prize(奖项)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>bone</v>
       </c>
       <c r="B38" t="str">
-        <v>bone</v>
+        <v>/boʊn/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D38" t="str">
         <v>骨架</v>
       </c>
-      <c r="D38" t="str">
-        <v>bone(骨架)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>send</v>
       </c>
       <c r="B39" t="str">
-        <v>send</v>
+        <v>/send/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D39" t="str">
         <v>发送</v>
       </c>
-      <c r="D39" t="str">
-        <v>send(发送)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>present</v>
       </c>
       <c r="B40" t="str">
-        <v>present</v>
+        <v>/ˈpreznt/</v>
       </c>
       <c r="C40" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D40" t="str">
         <v>展示</v>
       </c>
-      <c r="D40" t="str">
-        <v>present(展示)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>gain</v>
       </c>
       <c r="B41" t="str">
-        <v>gain</v>
+        <v>/ɡeɪn/</v>
       </c>
       <c r="C41" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D41" t="str">
         <v>收获</v>
       </c>
-      <c r="D41" t="str">
-        <v>gain(收获)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>umbrella</v>
       </c>
       <c r="B42" t="str">
-        <v>umbrella</v>
+        <v>/ʌmˈbrelə/</v>
       </c>
       <c r="C42" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>雨伞</v>
       </c>
-      <c r="D42" t="str">
-        <v>umbrella(雨伞)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>fortunate</v>
       </c>
       <c r="B43" t="str">
-        <v>fortunate</v>
+        <v>/ˈfɔːrtʃənət/</v>
       </c>
       <c r="C43" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D43" t="str">
         <v>幸运的</v>
       </c>
-      <c r="D43" t="str">
-        <v>fortunate(幸运的)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>fire</v>
       </c>
       <c r="B44" t="str">
-        <v>fire</v>
+        <v>/ˈfaɪər/</v>
       </c>
       <c r="C44" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D44" t="str">
         <v>火</v>
       </c>
-      <c r="D44" t="str">
-        <v>fire(火)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>prompt</v>
       </c>
       <c r="B45" t="str">
-        <v>prompt</v>
+        <v>/prɑːmpt/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./vt./v./adj./adv.</v>
+      </c>
+      <c r="D45" t="str">
         <v>迅速的</v>
       </c>
-      <c r="D45" t="str">
-        <v>prompt(迅速的)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>conservation</v>
       </c>
       <c r="B46" t="str">
-        <v>conservation</v>
+        <v>/ˌkɑːnsərˈveɪʃn/</v>
       </c>
       <c r="C46" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>保护</v>
       </c>
-      <c r="D46" t="str">
-        <v>conservation(保护)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>density</v>
       </c>
       <c r="B47" t="str">
-        <v>density</v>
+        <v>/ˈdensəti/</v>
       </c>
       <c r="C47" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>密度</v>
       </c>
-      <c r="D47" t="str">
-        <v>density(密度)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>Likewise</v>
       </c>
       <c r="B48" t="str">
-        <v>Likewise</v>
+        <v/>
       </c>
       <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
         <v>同样地</v>
       </c>
-      <c r="D48" t="str">
-        <v>Likewise(同样地)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>exit</v>
       </c>
       <c r="B49" t="str">
-        <v>exit</v>
+        <v>/ˈeksɪt,ˈeɡzɪt/</v>
       </c>
       <c r="C49" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D49" t="str">
         <v>出口</v>
       </c>
-      <c r="D49" t="str">
-        <v>exit(出口)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>near</v>
       </c>
       <c r="B50" t="str">
-        <v>near</v>
+        <v>/nɪr/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./adj./adv./prep.</v>
+      </c>
+      <c r="D50" t="str">
         <v>附近</v>
       </c>
-      <c r="D50" t="str">
-        <v>near(附近)📢</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>baggage</v>
       </c>
       <c r="B51" t="str">
-        <v>baggage</v>
+        <v>/ˈbæɡɪdʒ/</v>
       </c>
       <c r="C51" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>行李</v>
-      </c>
-      <c r="D51" t="str">
-        <v>baggage(行李)📢</v>
       </c>
     </row>
   </sheetData>
